--- a/artfynd/A 20987-2024 artfynd.xlsx
+++ b/artfynd/A 20987-2024 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>120974923</v>
       </c>
       <c r="B3" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 20987-2024 artfynd.xlsx
+++ b/artfynd/A 20987-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>114777376</v>
       </c>
       <c r="B2" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -712,7 +707,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Elisetorpslunden (Elisetorpslunden), Sk</t>
+          <t>Elisetorpslunden, Elisetorpslunden, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -788,72 +783,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120974923</v>
+        <v>116796812</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Elisetorpslunden, Elisetorpslunden, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>410790</v>
+        <v>410827</v>
       </c>
       <c r="R3" t="n">
-        <v>6200911</v>
+        <v>6200960</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,22 +848,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,6 +887,244 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120974923</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Elisetorpslunden, Elisetorpslunden, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>410790</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6200911</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jacob Björnberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jacob Björnberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>115411797</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Elisetorpslunden, Elisetorpslunden, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>410665</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6200912</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jacob Björnberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jacob Björnberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
